--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -47844,6 +47844,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2065">
+      <c r="A2065" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2065" t="n">
+        <v>63750</v>
+      </c>
+      <c r="C2065" t="n">
+        <v>0.307000011205673</v>
+      </c>
+      <c r="D2065" t="n">
+        <v>0.294999986886978</v>
+      </c>
+      <c r="E2065" t="n">
+        <v>0.303999990224838</v>
+      </c>
+      <c r="F2065" t="n">
+        <v>0.296999990940094</v>
+      </c>
+      <c r="G2065" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -47867,6 +47867,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2066">
+      <c r="A2066" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2066" t="n">
+        <v>24750</v>
+      </c>
+      <c r="C2066" t="n">
+        <v>0.307000011205673</v>
+      </c>
+      <c r="D2066" t="n">
+        <v>0.301999986171722</v>
+      </c>
+      <c r="E2066" t="n">
+        <v>0.307000011205673</v>
+      </c>
+      <c r="F2066" t="n">
+        <v>0.301999986171722</v>
+      </c>
+      <c r="G2066" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -47890,6 +47890,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2067">
+      <c r="A2067" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2067" t="n">
+        <v>49500</v>
+      </c>
+      <c r="C2067" t="n">
+        <v>0.308999985456467</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>0.296999990940094</v>
+      </c>
+      <c r="E2067" t="n">
+        <v>0.308999985456467</v>
+      </c>
+      <c r="F2067" t="n">
+        <v>0.296999990940094</v>
+      </c>
+      <c r="G2067" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -47913,6 +47913,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2068">
+      <c r="A2068" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2068" t="n">
+        <v>22500</v>
+      </c>
+      <c r="C2068" t="n">
+        <v>0.301999986171722</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>0.296999990940094</v>
+      </c>
+      <c r="E2068" t="n">
+        <v>0.301999986171722</v>
+      </c>
+      <c r="F2068" t="n">
+        <v>0.296999990940094</v>
+      </c>
+      <c r="G2068" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -47754,19 +47754,19 @@
     </row>
     <row r="2061">
       <c r="A2061" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2061" t="n">
-        <v>0</v>
+        <v>17250</v>
       </c>
       <c r="C2061" t="n">
         <v>0.303999990224838</v>
       </c>
       <c r="D2061" t="n">
-        <v>0.303999990224838</v>
+        <v>0.291999995708466</v>
       </c>
       <c r="E2061" t="n">
-        <v>0.303999990224838</v>
+        <v>0.29899999499321</v>
       </c>
       <c r="F2061" t="n">
         <v>0.303999990224838</v>
@@ -47777,22 +47777,22 @@
     </row>
     <row r="2062">
       <c r="A2062" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2062" t="n">
-        <v>33750</v>
+        <v>0</v>
       </c>
       <c r="C2062" t="n">
-        <v>0.305000007152557</v>
+        <v>0.303999990224838</v>
       </c>
       <c r="D2062" t="n">
-        <v>0.294999986886978</v>
+        <v>0.303999990224838</v>
       </c>
       <c r="E2062" t="n">
-        <v>0.300999999046326</v>
+        <v>0.303999990224838</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.305000007152557</v>
+        <v>0.303999990224838</v>
       </c>
       <c r="G2062" t="s">
         <v>7</v>
@@ -47800,19 +47800,19 @@
     </row>
     <row r="2063">
       <c r="A2063" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2063" t="n">
-        <v>41250</v>
+        <v>33750</v>
       </c>
       <c r="C2063" t="n">
-        <v>0.310000002384186</v>
+        <v>0.305000007152557</v>
       </c>
       <c r="D2063" t="n">
-        <v>0.296999990940094</v>
+        <v>0.294999986886978</v>
       </c>
       <c r="E2063" t="n">
-        <v>0.310000002384186</v>
+        <v>0.300999999046326</v>
       </c>
       <c r="F2063" t="n">
         <v>0.305000007152557</v>
@@ -47823,19 +47823,19 @@
     </row>
     <row r="2064">
       <c r="A2064" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2064" t="n">
-        <v>3750</v>
+        <v>41250</v>
       </c>
       <c r="C2064" t="n">
-        <v>0.30799999833107</v>
+        <v>0.310000002384186</v>
       </c>
       <c r="D2064" t="n">
-        <v>0.298000007867813</v>
+        <v>0.296999990940094</v>
       </c>
       <c r="E2064" t="n">
-        <v>0.30799999833107</v>
+        <v>0.310000002384186</v>
       </c>
       <c r="F2064" t="n">
         <v>0.305000007152557</v>
@@ -47846,22 +47846,22 @@
     </row>
     <row r="2065">
       <c r="A2065" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2065" t="n">
-        <v>63750</v>
+        <v>3750</v>
       </c>
       <c r="C2065" t="n">
-        <v>0.307000011205673</v>
+        <v>0.30799999833107</v>
       </c>
       <c r="D2065" t="n">
-        <v>0.294999986886978</v>
+        <v>0.298000007867813</v>
       </c>
       <c r="E2065" t="n">
-        <v>0.303999990224838</v>
+        <v>0.30799999833107</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.296999990940094</v>
+        <v>0.305000007152557</v>
       </c>
       <c r="G2065" t="s">
         <v>7</v>
@@ -47869,22 +47869,22 @@
     </row>
     <row r="2066">
       <c r="A2066" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2066" t="n">
-        <v>24750</v>
+        <v>63750</v>
       </c>
       <c r="C2066" t="n">
         <v>0.307000011205673</v>
       </c>
       <c r="D2066" t="n">
-        <v>0.301999986171722</v>
+        <v>0.294999986886978</v>
       </c>
       <c r="E2066" t="n">
-        <v>0.307000011205673</v>
+        <v>0.303999990224838</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.301999986171722</v>
+        <v>0.296999990940094</v>
       </c>
       <c r="G2066" t="s">
         <v>7</v>
@@ -47892,22 +47892,22 @@
     </row>
     <row r="2067">
       <c r="A2067" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2067" t="n">
-        <v>49500</v>
+        <v>24750</v>
       </c>
       <c r="C2067" t="n">
-        <v>0.308999985456467</v>
+        <v>0.307000011205673</v>
       </c>
       <c r="D2067" t="n">
-        <v>0.296999990940094</v>
+        <v>0.301999986171722</v>
       </c>
       <c r="E2067" t="n">
-        <v>0.308999985456467</v>
+        <v>0.307000011205673</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.296999990940094</v>
+        <v>0.301999986171722</v>
       </c>
       <c r="G2067" t="s">
         <v>7</v>
@@ -47915,24 +47915,47 @@
     </row>
     <row r="2068">
       <c r="A2068" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2068" t="n">
-        <v>22500</v>
+        <v>49500</v>
       </c>
       <c r="C2068" t="n">
-        <v>0.301999986171722</v>
+        <v>0.308999985456467</v>
       </c>
       <c r="D2068" t="n">
         <v>0.296999990940094</v>
       </c>
       <c r="E2068" t="n">
-        <v>0.301999986171722</v>
+        <v>0.308999985456467</v>
       </c>
       <c r="F2068" t="n">
         <v>0.296999990940094</v>
       </c>
       <c r="G2068" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2069" t="n">
+        <v>6750</v>
+      </c>
+      <c r="C2069" t="n">
+        <v>0.301999986171722</v>
+      </c>
+      <c r="D2069" t="n">
+        <v>0.301999986171722</v>
+      </c>
+      <c r="E2069" t="n">
+        <v>0.301999986171722</v>
+      </c>
+      <c r="F2069" t="n">
+        <v>0.301999986171722</v>
+      </c>
+      <c r="G2069" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -54221,6 +54221,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2072">
+      <c r="A2072" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2072" t="n">
+        <v>169500</v>
+      </c>
+      <c r="C2072" t="n">
+        <v>0.319999992847443</v>
+      </c>
+      <c r="D2072" t="n">
+        <v>0.307000011205673</v>
+      </c>
+      <c r="E2072" t="n">
+        <v>0.319999992847443</v>
+      </c>
+      <c r="F2072" t="n">
+        <v>0.310999989509583</v>
+      </c>
+      <c r="G2072" t="n">
+        <v>0.310999989509583</v>
+      </c>
+      <c r="H2072" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -54247,6 +54247,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2073">
+      <c r="A2073" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2073" t="n">
+        <v>109500</v>
+      </c>
+      <c r="C2073" t="n">
+        <v>0.310999989509583</v>
+      </c>
+      <c r="D2073" t="n">
+        <v>0.300999999046326</v>
+      </c>
+      <c r="E2073" t="n">
+        <v>0.310999989509583</v>
+      </c>
+      <c r="F2073" t="n">
+        <v>0.308999985456467</v>
+      </c>
+      <c r="G2073" t="n">
+        <v>0.308999985456467</v>
+      </c>
+      <c r="H2073" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -54273,6 +54273,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2074">
+      <c r="A2074" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2074" t="n">
+        <v>48000</v>
+      </c>
+      <c r="C2074" t="n">
+        <v>0.30799999833107</v>
+      </c>
+      <c r="D2074" t="n">
+        <v>0.300000011920929</v>
+      </c>
+      <c r="E2074" t="n">
+        <v>0.300999999046326</v>
+      </c>
+      <c r="F2074" t="n">
+        <v>0.30799999833107</v>
+      </c>
+      <c r="G2074" t="n">
+        <v>0.30799999833107</v>
+      </c>
+      <c r="H2074" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -54299,6 +54299,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2075">
+      <c r="A2075" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2075" t="n">
+        <v>28500</v>
+      </c>
+      <c r="C2075" t="n">
+        <v>0.324000000953674</v>
+      </c>
+      <c r="D2075" t="n">
+        <v>0.301999986171722</v>
+      </c>
+      <c r="E2075" t="n">
+        <v>0.324000000953674</v>
+      </c>
+      <c r="F2075" t="n">
+        <v>0.301999986171722</v>
+      </c>
+      <c r="G2075" t="n">
+        <v>0.301999986171722</v>
+      </c>
+      <c r="H2075" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -54377,6 +54377,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2078">
+      <c r="A2078" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2078" t="n">
+        <v>197250</v>
+      </c>
+      <c r="C2078" t="n">
+        <v>0.328999996185303</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>0.308999985456467</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>0.308999985456467</v>
+      </c>
+      <c r="F2078" t="n">
+        <v>0.32600000500679</v>
+      </c>
+      <c r="G2078" t="n">
+        <v>0.32600000500679</v>
+      </c>
+      <c r="H2078" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -48228,8 +48228,31 @@
       <c r="E2081" t="n">
         <v>0.314999997615814</v>
       </c>
-      <c r="F2081"/>
+      <c r="F2081" t="n">
+        <v>0.31700000166893</v>
+      </c>
       <c r="G2081" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2082" t="n">
+        <v>15750</v>
+      </c>
+      <c r="C2082" t="n">
+        <v>0.312999993562698</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>0.307000011205673</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>0.310000002384186</v>
+      </c>
+      <c r="F2082"/>
+      <c r="G2082" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -48251,8 +48251,31 @@
       <c r="E2082" t="n">
         <v>0.310000002384186</v>
       </c>
-      <c r="F2082"/>
+      <c r="F2082" t="n">
+        <v>0.312999993562698</v>
+      </c>
       <c r="G2082" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2083" t="n">
+        <v>15750</v>
+      </c>
+      <c r="C2083" t="n">
+        <v>0.319999992847443</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>0.310000002384186</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>0.314000010490417</v>
+      </c>
+      <c r="F2083"/>
+      <c r="G2083" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -48274,8 +48274,31 @@
       <c r="E2083" t="n">
         <v>0.314000010490417</v>
       </c>
-      <c r="F2083"/>
+      <c r="F2083" t="n">
+        <v>0.317999988794327</v>
+      </c>
       <c r="G2083" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2084" t="n">
+        <v>36000</v>
+      </c>
+      <c r="C2084" t="n">
+        <v>0.316000014543533</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>0.310999989509583</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>0.314000010490417</v>
+      </c>
+      <c r="F2084"/>
+      <c r="G2084" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -48297,7 +48297,9 @@
       <c r="E2084" t="n">
         <v>0.314000010490417</v>
       </c>
-      <c r="F2084"/>
+      <c r="F2084" t="n">
+        <v>0.316000014543533</v>
+      </c>
       <c r="G2084" t="s">
         <v>7</v>
       </c>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -48327,6 +48327,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2086">
+      <c r="A2086" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2086" t="n">
+        <v>123750</v>
+      </c>
+      <c r="C2086" t="n">
+        <v>0.319000005722046</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>0.312999993562698</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>0.316000014543533</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>0.319000005722046</v>
+      </c>
+      <c r="G2086" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -54663,6 +54663,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2089">
+      <c r="A2089" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2089" t="n">
+        <v>78750</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>0.321999996900558</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>0.314000010490417</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>0.319000005722046</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>0.321999996900558</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>0.321999996900558</v>
+      </c>
+      <c r="H2089" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -54689,6 +54689,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2090">
+      <c r="A2090" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2090" t="n">
+        <v>266250</v>
+      </c>
+      <c r="C2090" t="n">
+        <v>0.331000000238419</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>0.314999997615814</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>0.321999996900558</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="G2090" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="H2090" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -60988,6 +60988,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2091">
+      <c r="A2091" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2091" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2091" t="n">
+        <v>0.328999996185303</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="G2091" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="H2091" t="n">
+        <v>42000</v>
+      </c>
+      <c r="I2091" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2092" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2092" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>0.328999996185303</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>0.319999992847443</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>0.328999996185303</v>
+      </c>
+      <c r="G2092" t="n">
+        <v>0.328999996185303</v>
+      </c>
+      <c r="H2092" t="n">
+        <v>77250</v>
+      </c>
+      <c r="I2092" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -61046,6 +61046,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2093">
+      <c r="A2093" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2093" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2093" t="n">
+        <v>0.328999996185303</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>0.328999996185303</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>0.328999996185303</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>0.328999996185303</v>
+      </c>
+      <c r="G2093" t="n">
+        <v>0.328999996185303</v>
+      </c>
+      <c r="H2093" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2093" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2094" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2094" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>0.33500000834465</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>0.310999989509583</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>0.333000004291534</v>
+      </c>
+      <c r="G2094" t="n">
+        <v>0.333000004291534</v>
+      </c>
+      <c r="H2094" t="n">
+        <v>97500</v>
+      </c>
+      <c r="I2094" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -61104,6 +61104,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2095">
+      <c r="A2095" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2095" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2095" t="n">
+        <v>0.319999992847443</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>0.319999992847443</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>0.314000010490417</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="G2095" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="H2095" t="n">
+        <v>69750</v>
+      </c>
+      <c r="I2095" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -61115,7 +61115,7 @@
         <v>0.319999992847443</v>
       </c>
       <c r="D2095" t="n">
-        <v>0.319999992847443</v>
+        <v>0.330000013113022</v>
       </c>
       <c r="E2095" t="n">
         <v>0.314000010490417</v>
@@ -61130,6 +61130,35 @@
         <v>69750</v>
       </c>
       <c r="I2095" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2096" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2096" t="n">
+        <v>0.331999987363815</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>0.331999987363815</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>0.324999988079071</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>0.331000000238419</v>
+      </c>
+      <c r="G2096" t="n">
+        <v>0.331000000238419</v>
+      </c>
+      <c r="H2096" t="n">
+        <v>233250</v>
+      </c>
+      <c r="I2096" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -61162,6 +61162,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2097">
+      <c r="A2097" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2097" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2097" t="n">
+        <v>0.33899998664856</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>0.33899998664856</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>0.326999992132187</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>0.331000000238419</v>
+      </c>
+      <c r="G2097" t="n">
+        <v>0.331000000238419</v>
+      </c>
+      <c r="H2097" t="n">
+        <v>61500</v>
+      </c>
+      <c r="I2097" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -61191,6 +61191,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2098">
+      <c r="A2098" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2098" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2098" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>0.33899998664856</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>0.330000013113022</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>0.337999999523163</v>
+      </c>
+      <c r="G2098" t="n">
+        <v>0.337999999523163</v>
+      </c>
+      <c r="H2098" t="n">
+        <v>224250</v>
+      </c>
+      <c r="I2098" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -61202,7 +61202,7 @@
         <v>0.330000013113022</v>
       </c>
       <c r="D2098" t="n">
-        <v>0.33899998664856</v>
+        <v>0.340000003576279</v>
       </c>
       <c r="E2098" t="n">
         <v>0.330000013113022</v>
@@ -61217,6 +61217,35 @@
         <v>224250</v>
       </c>
       <c r="I2098" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2099" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2099" t="n">
+        <v>0.340999990701675</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>0.340999990701675</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>0.33899998664856</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>0.33899998664856</v>
+      </c>
+      <c r="G2099" t="n">
+        <v>0.33899998664856</v>
+      </c>
+      <c r="H2099" t="n">
+        <v>48000</v>
+      </c>
+      <c r="I2099" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SGC.MI.xlsx
+++ b/data/SGC.MI.xlsx
@@ -61249,6 +61249,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2100">
+      <c r="A2100" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2100" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2100" t="n">
+        <v>0.33899998664856</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>0.342999994754791</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>0.333000004291534</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>0.347000002861023</v>
+      </c>
+      <c r="G2100" t="n">
+        <v>0.347000002861023</v>
+      </c>
+      <c r="H2100" t="n">
+        <v>98250</v>
+      </c>
+      <c r="I2100" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
